--- a/word_dict_5.xlsx
+++ b/word_dict_5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/easy/Desktop/pol_r/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53529C7E-2E06-944A-9296-9889DE377987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE638923-D992-B64C-AF30-5901EA01174C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="580" yWindow="760" windowWidth="34560" windowHeight="20380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3747" uniqueCount="1839">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3748" uniqueCount="1839">
   <si>
     <t>rep</t>
   </si>
@@ -7465,6 +7465,9 @@
       <c r="F48" t="s">
         <v>139</v>
       </c>
+      <c r="G48" t="s">
+        <v>123</v>
+      </c>
       <c r="J48" t="s">
         <v>14</v>
       </c>
@@ -24503,7 +24506,7 @@
         <v>1445</v>
       </c>
       <c r="G576" t="s">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="J576" t="s">
         <v>14</v>
